--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table10.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table10.xlsx
@@ -55,11 +55,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="5">
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0\ ;\-#,##0\ ;&quot;-  &quot;"/>
-    <numFmt numFmtId="170" formatCode="#,###&quot; -r&quot;;\-#,###&quot; -r&quot;;&quot; -r&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0\ ;\-#,##0\ ;&quot;-  &quot;"/>
+    <numFmt numFmtId="167" formatCode="#,###&quot; -r&quot;;\-#,###&quot; -r&quot;;&quot; -r&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -126,10 +126,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -139,32 +139,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -664,22 +667,22 @@
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="N1"/>
@@ -1897,5 +1900,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>